--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col width="9.225" customWidth="1" min="1" max="1"/>
@@ -1284,75 +1284,6 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="6" t="n"/>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HeroSelectForm</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>res://TheGame/UIs/HeroSelectForm.tscn</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>HudForm</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>res://TheGame/UIs/HudForm.tscn</t>
-        </is>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GameOverForm</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>res://TheGame/UIs/GameOverForm.tscn</t>
-        </is>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="N1:O1"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col width="9.225" customWidth="1" min="1" max="1"/>
@@ -1284,6 +1284,29 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="6" t="n"/>
     </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BattleHud</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/BattleHud.tscn</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="N1:O1"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col width="9.225" customWidth="1" min="1" max="1"/>
@@ -1307,6 +1307,121 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>StartForm</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/start_form.tscn</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CharacterForm</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/character_form.tscn</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MapForm</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/map_form.tscn</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SettingsForm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/settings_form.tscn</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SaveForm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/save_form.tscn</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="N1:O1"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col width="9.225" customWidth="1" min="1" max="1"/>
@@ -1422,6 +1422,29 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SaveNoticeForm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>res://TheGame/UIs/save_notice_form.tscn</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="N1:O1"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R133830e325cd4753"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9dfd9d6c45f4563"/>
   </sheets>
 </workbook>
 </file>
@@ -1441,6 +1441,24 @@
         <v>Normal</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="str">
+        <v>SkillForm</v>
+      </c>
+      <c r="D15" t="str">
+        <v>res://TheGame/UIs/skill_form.tscn</v>
+      </c>
+      <c r="E15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="N1:O1"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1250,12 +1250,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BattleHud</t>
+          <t>BattleForm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">res://TheGame/UIs/BattleHud.tscn</t>
+          <t>res://TheGame/UIs/BattleForm.tscn</t>
         </is>
       </c>
       <c r="E6" t="b">
